--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16980"/>
+    <workbookView windowWidth="23040" windowHeight="10188"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,15 +137,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -620,12 +620,12 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -750,15 +750,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,7 +775,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1147,12 +1150,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultColWidth="8.88571428571429" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.21904761904762" customWidth="1"/>
+    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
     <col min="2" max="2" width="13.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="17.6666666666667" customWidth="1"/>
-    <col min="4" max="5" width="22.552380952381" customWidth="1"/>
+    <col min="4" max="5" width="22.5555555555556" customWidth="1"/>
     <col min="7" max="7" width="20.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1205,10 +1208,10 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1219,7 +1222,7 @@
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D2" t="s">
@@ -1228,7 +1231,7 @@
       <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1258,13 +1261,13 @@
       <c r="O2" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="2" t="s">
         <v>26</v>
       </c>
     </row>

--- a/testdata/configuration.xlsx
+++ b/testdata/configuration.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10188"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
